--- a/ig/DM-OCTOBRE-2026/ValueSet-JDV-J56-AuthorSpecialty-DMP.xlsx
+++ b/ig/DM-OCTOBRE-2026/ValueSet-JDV-J56-AuthorSpecialty-DMP.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="815" uniqueCount="777">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="841">
   <si>
     <t>Property</t>
   </si>
@@ -40,7 +40,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20240927120000</t>
+    <t>20261102120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-27T12:00:00+01:00</t>
+    <t>2026-11-02T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2293,10 +2293,16 @@
     <t>329</t>
   </si>
   <si>
+    <t>330</t>
+  </si>
+  <si>
+    <t>Coordonnateur de parcours</t>
+  </si>
+  <si>
     <t>331</t>
   </si>
   <si>
-    <t>Secrétaire médicale</t>
+    <t>Secrétaire assistante médico-administrative</t>
   </si>
   <si>
     <t>332</t>
@@ -2323,28 +2329,214 @@
     <t>Gestionnaire alertes et urgences sanitaires</t>
   </si>
   <si>
-    <t>350</t>
+    <t>336</t>
+  </si>
+  <si>
+    <t>Autre professionnel intervenant dans l'accueil et l'orientation des personnes</t>
+  </si>
+  <si>
+    <t>337</t>
+  </si>
+  <si>
+    <t>Autre professionnel intervenant dans la logistique</t>
+  </si>
+  <si>
+    <t>338</t>
+  </si>
+  <si>
+    <t>Autre professionnel intervenant dans l'hôtellerie et la restauration</t>
+  </si>
+  <si>
+    <t>339</t>
+  </si>
+  <si>
+    <t>Autre professionnel intervenant dans la direction de la qualité, hygiène, sécurité et environnement</t>
+  </si>
+  <si>
+    <t>340</t>
+  </si>
+  <si>
+    <t>Autre professionnel intervenant dans la direction des systèmes d'information</t>
+  </si>
+  <si>
+    <t>341</t>
+  </si>
+  <si>
+    <t>Autre professionnel intervenant dans la direction des finances et comptabilité</t>
+  </si>
+  <si>
+    <t>342</t>
+  </si>
+  <si>
+    <t>Autre professionnel intervenant dans la direction de la communication</t>
+  </si>
+  <si>
+    <t>343</t>
+  </si>
+  <si>
+    <t>Autre professionnel intervenant dans la direction des ressources humaines</t>
+  </si>
+  <si>
+    <t>344</t>
+  </si>
+  <si>
+    <t>Autre professionnel intervenant dans la direction des affaires médicales</t>
+  </si>
+  <si>
+    <t>345</t>
+  </si>
+  <si>
+    <t>Autre professionnel intervenant dans le social, éducatif, psychologie et culturel</t>
+  </si>
+  <si>
+    <t>346</t>
+  </si>
+  <si>
+    <t>Etudiant - infirmier</t>
+  </si>
+  <si>
+    <t>347</t>
+  </si>
+  <si>
+    <t>Etudiant - aide-soignant</t>
+  </si>
+  <si>
+    <t>348</t>
+  </si>
+  <si>
+    <t>Etudiant - auxiliaire de puériculture</t>
+  </si>
+  <si>
+    <t>349</t>
+  </si>
+  <si>
+    <t>Etudiant - masseur-kinésithérapeute</t>
+  </si>
+  <si>
+    <t>351</t>
+  </si>
+  <si>
+    <t>Assistant(e) maternel(le)</t>
+  </si>
+  <si>
+    <t>352</t>
+  </si>
+  <si>
+    <t>Autre salarié de la structure sociale</t>
+  </si>
+  <si>
+    <t>353</t>
+  </si>
+  <si>
+    <t>Membre de l'équipe de soins</t>
+  </si>
+  <si>
+    <t>354</t>
+  </si>
+  <si>
+    <t>Externe en médecine</t>
+  </si>
+  <si>
+    <t>355</t>
+  </si>
+  <si>
+    <t>Externe en odontologie</t>
+  </si>
+  <si>
+    <t>356</t>
+  </si>
+  <si>
+    <t>Externe en maïeutique</t>
+  </si>
+  <si>
+    <t>357</t>
+  </si>
+  <si>
+    <t>Externe en pharmacie</t>
+  </si>
+  <si>
+    <t>358</t>
+  </si>
+  <si>
+    <t>Autre étudiant</t>
+  </si>
+  <si>
+    <t>359</t>
+  </si>
+  <si>
+    <t>Directeur d'établissement</t>
+  </si>
+  <si>
+    <t>360</t>
+  </si>
+  <si>
+    <t>Brancardier</t>
+  </si>
+  <si>
+    <t>361</t>
+  </si>
+  <si>
+    <t>Educateur en activité physique adaptée</t>
+  </si>
+  <si>
+    <t>362</t>
+  </si>
+  <si>
+    <t>Technicien d'informations médicales</t>
+  </si>
+  <si>
+    <t>363</t>
+  </si>
+  <si>
+    <t>Attaché de recherche clinique</t>
+  </si>
+  <si>
+    <t>364</t>
+  </si>
+  <si>
+    <t>Praticien A Diplôme Hors Union Européenne (PADHUE)</t>
+  </si>
+  <si>
+    <t>365</t>
+  </si>
+  <si>
+    <t>Gestionnaire admissions / frais de séjour / traitement externe</t>
+  </si>
+  <si>
+    <t>366</t>
+  </si>
+  <si>
+    <t>Archiviste</t>
+  </si>
+  <si>
+    <t>367</t>
+  </si>
+  <si>
+    <t>Surveillant de nuit</t>
+  </si>
+  <si>
+    <t>368</t>
+  </si>
+  <si>
+    <t>Animateur</t>
+  </si>
+  <si>
+    <t>370</t>
+  </si>
+  <si>
+    <t>Opérateur de Soins Non Programmés</t>
+  </si>
+  <si>
+    <t>371</t>
+  </si>
+  <si>
+    <t>Aide à domicile qualifié(e)</t>
+  </si>
+  <si>
+    <t>372</t>
   </si>
   <si>
     <t>Aide à domicile</t>
-  </si>
-  <si>
-    <t>351</t>
-  </si>
-  <si>
-    <t>Assistant(e) maternel(le)</t>
-  </si>
-  <si>
-    <t>352</t>
-  </si>
-  <si>
-    <t>Autre salarié de la structure sociale</t>
-  </si>
-  <si>
-    <t>353</t>
-  </si>
-  <si>
-    <t>Membre de l'équipe de soins</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/TRE_R85-RolePriseCharge/FHIR/TRE-R85-RolePriseCharge</t>
@@ -5481,7 +5673,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:B74"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -5810,18 +6002,274 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>40</v>
+        <v>776</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>40</v>
+        <v>777</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
+        <v>778</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>780</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>782</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>784</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>786</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>788</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>790</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>792</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>794</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>796</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>798</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>800</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>802</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>804</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>806</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>808</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>810</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>812</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>814</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>816</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>818</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>820</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>822</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>824</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>826</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>828</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>830</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
+        <v>832</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="2">
+        <v>834</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
+        <v>836</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="2">
+        <v>838</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="2">
         <v>41</v>
       </c>
-      <c r="B42" t="s" s="2">
-        <v>776</v>
+      <c r="B74" t="s" s="2">
+        <v>840</v>
       </c>
     </row>
   </sheetData>
